--- a/artfynd/A 35618-2025 artfynd.xlsx
+++ b/artfynd/A 35618-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129992612</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35618-2025 artfynd.xlsx
+++ b/artfynd/A 35618-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129992612</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
